--- a/output/2026-09-02_02_Italia_Abruzzo_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-02_02_Italia_Abruzzo_Impiantistica_aspirazione_industriale.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vendita e assistenza aspiratori industriali, trattamento aria, idropulitrici, macchine industriali. Verificato su Virgilio, PagineBianche, sito proprio.</t>
+          <t>Vendita e assistenza aspiratori industriali, trattamento aria, idropulitrici, macchine industriali. Verificato su Virgilio, PagineBianche, sito proprio. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sede legale fuori Abruzzo ma copertura B2B in regione confermata da fonte propria (opera anche in PE/AQ/TE). Da valutare come distributore extraregionale con copertura locale.</t>
+          <t>Sede legale fuori Abruzzo ma copertura B2B in regione confermata da fonte propria (opera anche in PE/AQ/TE). Da valutare come distributore extraregionale con copertura locale. [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
